--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLV/LTAIPT_A63F45B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLV/LTAIPT_A63F45B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE080ACD-5435-4AEF-93BE-EAB1FEFC3C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A32B6DC-FE37-4007-9CC6-318E0BE45D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="66">
   <si>
     <t>59951</t>
   </si>
@@ -156,22 +156,7 @@
     <t>Del 01 de julio del 2024 al 31 de diciembre del 2024, el Colegio de Bachilleres del Estado de Tlaxcala, no genero índice de expedientes clasificados como reservados, lo anterior de acuerdo a los artículos 92, 93 y 94 de la Ley de Transparencia y Acceso a la Información Pública  del Estado de Tlaxcala.</t>
   </si>
   <si>
-    <t>0EBC51E465AA685ECB96E7F5A68FB4B7</t>
-  </si>
-  <si>
-    <t>01/01/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
     <t>10184333</t>
-  </si>
-  <si>
-    <t>30/04/2024</t>
-  </si>
-  <si>
-    <t>Del 01 de enero del 2024 al 30 de junio del 2024, el Colegio de Bachilleres del Estado de Tlaxcala, no genero indice de expedientes clasificados como reservados, lo anterior de acuerdo a los artìculos 92, 93 y 94 de la Ley de Transparencia y Acceso a la Información Pública  del Estado de Tlaxcala.</t>
   </si>
   <si>
     <t>81011</t>
@@ -649,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
@@ -834,38 +819,6 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A6:J6"/>
@@ -877,7 +830,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E201" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E200" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -937,46 +890,46 @@
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" t="s">
         <v>48</v>
-      </c>
-      <c r="D2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -984,51 +937,51 @@
         <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1048,12 +1001,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
